--- a/4.evidence/ITGC/ChangeManagement_Register_FY2025.xlsx
+++ b/4.evidence/ITGC/ChangeManagement_Register_FY2025.xlsx
@@ -443,8 +443,8 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -500,12 +500,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>承認者1(情シス)</t>
+          <t>承認者1(情シス:役職付)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>承認者2(業務)</t>
+          <t>承認者2(業務:役職付)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>岡田 宏 (IT001)</t>
+          <t>岡田 宏 (IT001/E0051) 情報システム部長</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>岡田 宏 (IT001)</t>
+          <t>岡田 宏 (IT001/E0051) 情報システム部長</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>岡田 宏 (IT001)</t>
+          <t>岡田 宏 (IT001/E0051) 情報システム部長</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>岡田 宏 (IT001)</t>
+          <t>岡田 宏 (IT001/E0051) 情報システム部長</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>岡田 宏 (IT001)</t>
+          <t>岡田 宏 (IT001/E0051) 情報システム部長</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>加藤 洋子 (IT003)</t>
+          <t>加藤 洋子 (IT003/E0053) アプリチームリーダー</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>業務部門長</t>
+          <t>業務部門長 / 業務部門長</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
